--- a/LLM_Extraction_and_CrossCritique/interactive-table/gt-vs-runs_pipeline2.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/gt-vs-runs_pipeline2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="386">
   <si>
     <t>Query</t>
   </si>
@@ -2070,7 +2070,271 @@
   <si>
     <t>{
   "selected_filter": {
+    "Class of ICI": "PD-1",
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Melanoma",
+    "Monotherapy/combination": "Combination Therapy",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Clinical setting in relation to surgery",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Type of combination",
+    "Column 10": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "CTLA-4",
+    "Cancer type": "Esophageal/GEJ"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Total sample size",
+    "Column 7": "Class of ICI",
+    "Column 8": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial phase": "Phase 3",
+    "Monotherapy/combination": "Monotherapy",
+    "Cancer type": "Urothelial"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Trial phase",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
     "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Adjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Clinical setting in relation to surgery",
+    "Column 7": "Study name",
+    "Column 8": "Trial phase",
+    "Column 9": "Name of ICI",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "['PD-1', 'CTLA-4']",
+    "Cancer type": "Renal Cell Carcinoma (RCC)",
+    "Type of combination (Treatment Arm)": "ICI + ICI",
+    "Control Arm": "TKI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Control regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Cancer type",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Type of combination",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Control regimen",
+    "Column 7": "Primary endpoint",
+    "Column 8": "Cancer type",
+    "Column 9": "Name of ICI",
+    "Column 10": "Class of ICI"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "PD-1",
+    "Monotherapy/combination": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Class of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Secondary endpoint",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "PD-L1",
+    "Monotherapy/combination": "Combination Therapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Type of combination",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "CTLA-4",
+    "Monotherapy/combination": "Monotherapy",
+    "Cancer type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Cancer type",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "CTLA-4",
+    "Monotherapy/combination": "Combination Therapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Head and Neck (HNSCC)",
     "Class of ICI": "PD-1"
   },
   "selected_column": {
@@ -2078,10 +2342,193 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial phase": "Phase 3",
+    "ICI Name": "Pembrolizumab",
+    "Cancer type": "NSCLC"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Trial phase",
+    "Column 7": "Name of ICI",
+    "Column 8": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Nivolumab",
+    "Cancer type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
     "Column 5": "Name of ICI",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Atezolizumab",
+    "Type of combination (Treatment Arm)": "ICI + Chemo",
+    "Cancer type": "Breast"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Monotherapy/combination",
+    "Column 7": "Type of combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Cancer type",
+    "Column 10": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Avelumab",
+    "Cancer type": "Bladder"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Clinical setting in relation to surgery",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Trial phase",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Tremelimumab",
+    "Cancer type": "Hepatocellular carcinoma (HCC)",
+    "Monotherapy/combination": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Class of ICI",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Durvalumab",
+    "Cancer type": "NSCLC",
+    "Clinical Setting": "Maintenance",
+    "Trial phase": "Phase 3",
+    "Control Arm": "Placebo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Clinical setting in relation to surgery",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial phase": "Phase 3",
+    "Class of ICI": "PD-1",
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Monotherapy/combination": "Combination Therapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Total sample size",
+    "Column 6": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "PD-L1",
+    "Monotherapy/combination": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Cancer type",
+    "Column 9": "Study name",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + ICI",
+    "Cancer type": "['Melanoma', 'Mesothelioma', 'Renal Cell Carcinoma (RCC)']"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Class of ICI",
+    "Column 7": "Type of combination",
+    "Column 8": "Name of ICI",
     "Column 9": "Treatment regimen",
     "Column 10": "Trial phase"
   }
@@ -2090,39 +2537,154 @@
   <si>
     <t>{
   "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Name of ICI",
+    "Column 7": "Type of combination",
+    "Column 8": "Cancer type",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + TKI",
+    "Cancer type": "Renal Cell Carcinoma (RCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + RadiatICln"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Monotherapy/combination",
+    "Column 7": "Type of combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Cancer type",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + Vaccine"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Type of combination",
+    "Column 9": "Cancer type",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
     "Cancer type": "Melanoma",
-    "Monotherapy/combination": "Combination",
-    "Type of combination": "ICI + ICI"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Clinical setting in relation to surgery",
-    "Column 6": "Study name",
+    "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Class of ICI",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + Anti-VEGF"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Type of combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Cancer type",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + Chemo + Anti-VEGF",
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Treatment regimen",
     "Column 7": "Name of ICI",
     "Column 8": "Class of ICI",
     "Column 9": "Type of combination",
-    "Column 10": "Primary endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Gastric/GEJ",
-    "Class of ICI": "CTLA-4"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Total sample size",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Name of ICI",
     "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
+    "Column 8": "Type of combination",
     "Column 9": "Cancer type",
     "Column 10": "Trial phase"
   }
@@ -2131,10 +2693,8 @@
   <si>
     <t>{
   "selected_filter": {
-    "Cancer type": "Urothelial",
     "Trial phase": "Phase 3",
-    "Monotherapy/combination": "Monotherapy",
-    "Type of Study": "Follow-up"
+    "Type of control": "Placebo"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -2142,19 +2702,740 @@
     "Column 3": "Authors",
     "Column 4": "Year",
     "Column 5": "Trial phase",
+    "Column 6": "Class of ICI",
+    "Column 7": "Name of ICI",
+    "Column 8": "Type of control",
+    "Column 9": "Control regimen",
+    "Column 10": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Control Arm": "Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Control regimen",
+    "Column 7": "Type of control",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Name of ICI",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Hepatocellular carcinoma (HCC)",
+    "Control Arm": "TKI (Tyrosine Kinase Inhibitor)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Control regimen",
+    "Column 7": "Type of control"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Interferon"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Trial phase",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Best Supportive Care (BSC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Trial phase",
+    "Column 8": "Control regimen",
+    "Column 9": "Type of control",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Chemo / Anti-EGFR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Control regimen",
+    "Column 8": "Cancer type",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Chemo / Anti-VEGF"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Trial phase",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Type of control"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "mTOR inhibitor",
+    "Cancer type": "Renal Cell Carcinoma (RCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Cancer type",
+    "Column 7": "Type of control",
+    "Column 8": "Trial phase",
+    "Column 9": "Name of ICI",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Multikinase inhibitor"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Class of ICI",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Vaccine"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Type of control",
+    "Column 7": "Study name",
+    "Column 8": "Cancer type",
+    "Column 9": "Trial phase",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Radiation"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Type of control",
+    "Column 7": "Cancer type",
+    "Column 8": "Clinical setting in relation to surgery",
+    "Column 9": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Melanoma",
+    "Clinical Setting": "Adjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Clinical setting in relation to surgery",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Trial phase",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Neoadjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Clinical setting in relation to surgery",
+    "Column 7": "Primary endpoint",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Name of ICI",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "Path CR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Clinical setting in relation to surgery",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
+    "Column 9": "Study name",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "ORR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Trial phase",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Study name",
+    "Column 7": "Trial phase",
+    "Column 8": "Cancer type",
+    "Column 9": "Total sample size",
+    "Column 10": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "PFS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Trial phase",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "RFS (Recurrence-/Relapse-Free Survival)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Follow-up duration for primary endpoint(s) in months",
+    "Column 7": "Clinical setting in relation to surgery",
+    "Column 8": "Cancer type",
+    "Column 9": "Trial phase",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "EFS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Primary multiple, composite, or co-primary endpoints?"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "Safety"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Trial phase",
+    "Column 7": "Total sample size",
+    "Column 8": "Cancer type",
+    "Column 9": "Name of ICI",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Is PD-L1 positivity inclusion criteria",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Lines of treatment"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Colorectal",
+    "Is any other biomarker used for inclusion": "MSI-H/dMMR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Is any other biomarker used for inclusion",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Lines of treatment"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Pancreatic Cancer"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Is PD-L1 positivity inclusion criteria",
+    "Column 10": "Is any other biomarker used for inclusion"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Prostate"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Trial phase",
+    "Column 9": "Is PD-L1 positivity inclusion criteria",
+    "Column 10": "Is any other biomarker used for inclusion"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Multiple Myeloma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Primary endpoint",
+    "Column 8": "Trial phase",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Mesothelioma",
+    "Monotherapy/combination": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Control regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Class of ICI",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Original publication or Follow-up",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Original publication or Follow-up",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Class of ICI",
+    "Column 9": "Follow-up duration for primary endpoint(s) in months",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Trial phase",
+    "Column 6": "Primary multiple, composite, or co-primary endpoints?",
+    "Column 7": "Primary endpoint",
+    "Column 8": "Study name",
+    "Column 9": "Cancer type",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Follow-up duration for primary endpoint(s) in months",
+    "Column 7": "Type of follow-up given",
+    "Column 8": "Study name",
+    "Column 9": "Original/Follow Up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "PFS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Follow-up duration for primary endpoint(s) in months",
+    "Column 7": "Type of follow-up given"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Number of arms",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Lines of treatment",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Bladder",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Lines of treatment",
+    "Column 7": "Name of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Head and Neck (HNSCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Trial phase",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Pembrolizumab",
+    "Cancer type": "NSCLC",
+    "Control Arm": "Chemo",
+    "Trial phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Control regimen",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Melanoma",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Type of combination",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Secondary endpoint",
     "Column 6": "Primary endpoint",
-    "Column 7": "Original/Follow up",
-    "Column 8": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
     "Column 9": "Name of ICI",
-    "Column 10": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Clinical setting in relation to surgery": "Adjuvant"
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Original publication or Follow-up",
+    "Column 6": "Primary endpoint",
+    "Column 7": "Secondary endpoint",
+    "Column 8": "Type of follow-up given",
+    "Column 9": "Follow-up duration for primary endpoint(s) in months",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Included in MA": "Yes"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -2162,28 +3443,87 @@
     "Column 3": "Authors",
     "Column 4": "Year",
     "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
     "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Renal Cell Carcinoma (RCC)",
-    "Class of ICI": "PD-1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Included in MA": "No"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Trial phase",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Total sample size",
+    "Column 10": "Original/Follow Up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Renal Cell Carcinoma (RCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Original publication or Follow-up",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Trial phase",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial phase": "Phase 3",
+    "Cancer type": "Gastric/GEJ",
+    "Class of ICI": "PD-L1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Class of ICI",
+    "Column 7": "Name of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "PD-1",
+    "Cancer type": "Esophageal/GEJ"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
     "Column 8": "Study name",
     "Column 9": "Trial phase",
     "Column 10": "Treatment regimen"
@@ -2193,18 +3533,211 @@
   <si>
     <t>{
   "selected_filter": {
-    "Class of ICI": "PD-L1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
+    "Cancer type": "Small Cell Lung Cancer (SCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Secondary endpoint",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Head and Neck (HNSCC)",
+    "Primary Endpoint": "OS (Overall Survival)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Primary endpoint",
+    "Column 7": "Study name",
+    "Column 8": "Trial phase",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Head and Neck (HNSCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Trial phase",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Class of ICI",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Breast"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Class of ICI",
+    "Column 8": "Trial phase",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Gastric/GEJ",
+    "Clinical Setting": "second-line+"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Lines of treatment",
     "Column 7": "Name of ICI",
-    "Column 8": "Trial phase",
-    "Column 9": "Class of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Hepatocellular carcinoma (HCC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Lines of treatment",
+    "Column 7": "Name of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Renal Cell Carcinoma (RCC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Clinical Setting": "Perioperative"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Clinical setting in relation to surgery",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Type of combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Class of ICI",
+    "Column 7": "Lines of treatment",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Trial phase",
+    "Column 8": "Cancer type",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + MEKi"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
     "Column 10": "Cancer type"
   }
 }</t>
@@ -2212,35 +3745,56 @@
   <si>
     <t>{
   "selected_filter": {
-    "Total sample size": "&gt;= 500"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Total sample size"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "OS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
+    "Cancer type": "NSCLC"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Monotherapy/combination",
+    "Column 7": "Name of ICI",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Head and Neck (HNSCC)",
+    "Monotherapy/combination": "Combination Therapy",
+    "Class of ICI": "PD-1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Monotherapy/combination",
+    "Column 7": "Type of combination",
     "Column 8": "Name of ICI",
     "Column 9": "Class of ICI",
     "Column 10": "Treatment regimen"
@@ -2250,86 +3804,47 @@
   <si>
     <t>{
   "selected_filter": {
-    "Year": "&gt; 2020"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Is PD-L1 positivity inclusion criteria": "No"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Is PD-L1 positivity inclusion criteria",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Trial phase",
     "Column 7": "Class of ICI",
     "Column 8": "Name of ICI",
-    "Column 9": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "PD-1",
-    "Monotherapy/combination": "Monotherapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Name of ICI",
-    "Column 7": "Class of ICI",
-    "Column 8": "Study name",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "PD-L1",
-    "Monotherapy/combination": "Combination"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Study name",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "CTLA-4",
-    "Monotherapy/combination": "Monotherapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Study name",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "CTLA-4",
-    "Monotherapy/combination": "Combination"
+    "Column 9": "Study name",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Renal Cell Carcinoma (RCC)",
+    "Type of combination (Treatment Arm)": "ICI + TKI"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -2338,1673 +3853,52 @@
     "Column 4": "Year",
     "Column 5": "Name of ICI",
     "Column 6": "Class of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Study name",
-    "Column 9": "Trial phase",
-    "Column 10": "Monotherapy/combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Head and Neck (HNSCC)",
-    "Class of ICI": "PD-1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Class of ICI",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial phase": "Phase 3",
+    "Column 7": "Cancer type",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Small Cell Lung Cancer (SCLC)",
+    "Monotherapy/combination": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + Chemo",
+    "Class of ICI": "PD-L1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
     "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Class of ICI": "PD-1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Trial phase",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Class of ICI",
-    "Column 9": "Study name",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Melanoma",
-    "Class of ICI": "PD-1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Study name",
-    "Column 9": "Trial phase",
-    "Column 10": "Monotherapy/combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Breast",
-    "Class of ICI": "PD-L1",
-    "Monotherapy/combination": "Combination",
-    "Type of combination": "ICI + Chemo",
-    "Is PD-L1 positivity inclusion criteria": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Trial phase",
-    "Column 9": "Class of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Urothelial",
-    "Class of ICI": "PD-L1",
-    "Clinical setting in relation to surgery": "Maintenance",
-    "Lines of treatment": "1L"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Class of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Hepatocellular carcinoma (HCC)",
-    "Class of ICI": "CTLA-4",
-    "Monotherapy/combination": "Combination",
-    "Type of combination": "ICI + ICI"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Class of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Trial phase": "Phase 3",
-    "Monotherapy/combination": "Monotherapy",
-    "Clinical setting in relation to surgery": "Maintenance",
-    "Class of ICI": "PD-L1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Trial phase",
-    "Column 9": "Treatment regimen",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial phase": "Phase 3",
-    "Class of ICI": "PD-1",
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Monotherapy/combination": "Combination"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Monotherapy/combination",
-    "Column 7": "Total sample size",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Study name"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "PD-L1",
-    "Monotherapy/combination": "Monotherapy"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Study name",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + ICI",
-    "Class of ICI": "PD-1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Class of ICI",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of combination": "ICI + Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Trial phase",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + TKI"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Trial phase",
-    "Column 8": "Study name",
-    "Column 9": "Class of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + Radiation"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Type of combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + Vaccine"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Type of combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Melanoma",
-    "Type of combination": "ICI + BRAFi + MEKi"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Cancer type",
-    "Column 10": "Type of combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + Anti-VEGF"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Type of combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + Chemo + Anti-VEGF"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Class of ICI",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + ICI + Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Treatment regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial phase": "Phase 3",
-    "Type of control": "Placebo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Trial phase",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Study name",
-    "Column 9": "Name of ICI",
-    "Column 10": "Type of control"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of control": "Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Type of control"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Hepatocellular carcinoma (HCC)",
-    "Type of control": "TKI"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Class of ICI",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Interferon",
-    "Cancer type": "Renal Cell Carcinoma (RCC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Class of ICI",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Best Supportive Care"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Type of control"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Chemo / Anti-EGFR"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Class of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Control regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Chemo / Anti-VEGF"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Class of ICI",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Type of control"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Renal Cell Carcinoma (RCC)",
-    "Type of control": "mTOR inhibitor"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Class of ICI",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Multikinase inhibitor"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Control regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Vaccine"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Type of control"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Radiation"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Class of ICI",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Type of control"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Melanoma",
-    "Clinical setting in relation to surgery": "Adjuvant"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Class of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Clinical setting in relation to surgery": "Neoadjuvant"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "Path CR",
-    "Clinical setting in relation to surgery": "Adjuvant"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI",
-    "Column 10": "Clinical setting in relation to surgery"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "ORR"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "OS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "PFS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "RFS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "EFS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "Safety"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Is PD-L1 positivity inclusion criteria": "Yes",
-    "Class of ICI": "PD-L1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Is PD-L1 positivity inclusion criteria",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Study name",
-    "Column 9": "Name of ICI",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Colorectal"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Pancreatic Cancer",
-    "Is any other biomarker used for inclusion": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Is any other biomarker used for inclusion",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Study name",
-    "Column 9": "Name of ICI",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Prostate"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Trial phase",
-    "Column 8": "Study name",
-    "Column 9": "Class of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Multiple Myeloma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Trial phase",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Mesothelioma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Name of ICI",
-    "Column 8": "Trial phase",
-    "Column 9": "Cancer type",
-    "Column 10": "Treatment regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Trial phase",
-    "Column 7": "Original/Follow up",
-    "Column 8": "Study name",
-    "Column 9": "Name of ICI",
-    "Column 10": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Melanoma",
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Original/Follow up",
-    "Column 6": "Study name",
-    "Column 7": "Name of ICI",
-    "Column 8": "Primary endpoint",
-    "Column 9": "Trial phase",
-    "Column 10": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial phase": "Phase 3"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "OS",
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Trial phase",
-    "Column 7": "Original/Follow up",
-    "Column 8": "Study name",
-    "Column 9": "Name of ICI",
-    "Column 10": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "PFS",
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Trial phase",
-    "Column 7": "Original/Follow up",
-    "Column 8": "Study name",
-    "Column 9": "Name of ICI",
-    "Column 10": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Number of arms"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Lines of treatment": "1L"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Class of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Lines of treatment"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Bladder",
-    "Lines of treatment": "2L"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Head and Neck (HNSCC)",
-    "Year": "2023+"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Trial phase",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Class of ICI": "PD-1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Melanoma",
-    "Monotherapy/combination": "Combination",
-    "Class of ICI": "PD-1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI",
-    "Column 10": "Secondary endpoint"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
-    "Column 8": "Original/Follow up",
-    "Column 9": "Name of ICI",
-    "Column 10": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Included in MA": "Yes"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Included in MA": "No"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Renal Cell Carcinoma (RCC)",
-    "Type of Study": "Original publication"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Trial phase",
-    "Column 8": "Original/Follow up",
-    "Column 9": "Name of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial phase": "Phase 3",
-    "Cancer type": "Gastric/GEJ",
-    "Class of ICI": "PD-L1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Trial phase",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Class of ICI",
-    "Column 9": "Name of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Esophageal/GEJ",
-    "Class of ICI": "PD-1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Class of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Small Cell Lung Cancer (SCLC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Name of ICI",
-    "Column 8": "Trial phase",
-    "Column 9": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Head and Neck (HNSCC)",
-    "Primary endpoint": "OS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Head and Neck (HNSCC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Class of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Study name",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Breast"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Class of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Gastric/GEJ",
-    "Lines of treatment": "2L"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Trial phase",
-    "Column 9": "Class of ICI",
-    "Column 10": "Lines of treatment"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Hepatocellular carcinoma (HCC)",
-    "Lines of treatment": "1L"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Class of ICI",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Renal Cell Carcinoma (RCC)",
-    "Lines of treatment": "1L"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Class of ICI",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Clinical setting in relation to surgery": "Perioperative"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Lines of treatment": "2L"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Class of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Lines of treatment"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {},
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Class of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Study name",
-    "Column 9": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of combination": "ICI + MEKi"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Class of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Type of combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Class of ICI": "PD-1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Class of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Study name",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Melanoma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Monotherapy/combination",
-    "Column 6": "Study name",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Class of ICI",
-    "Column 9": "Name of ICI",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Head and Neck (HNSCC)",
-    "Monotherapy/combination": "Combination"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Trial phase",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Is PD-L1 positivity inclusion criteria": "No",
-    "Class of ICI": "PD-L1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial phase": "Phase 3"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Trial phase",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Study name",
-    "Column 9": "Name of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Renal Cell Carcinoma (RCC)",
-    "Type of combination": "ICI + TKI"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
+    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Treatment regimen",
     "Column 7": "Name of ICI",
     "Column 8": "Class of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Small Cell Lung Cancer (SCLC)",
-    "Type of combination": "ICI + Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of combination": "ICI + ICI + Chemo"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Class of ICI",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Year": "2010–2012"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Class of ICI",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Class of ICI": "PD-1",
-    "Monotherapy/combination": "Combination",
-    "Type of combination": "ICI + ICI"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Class of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Lines of treatment": "3L"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Trial phase",
-    "Column 8": "Original/Follow up",
-    "Column 9": "Name of ICI",
-    "Column 10": "Class of ICI"
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Type of combination"
   }
 }</t>
   </si>
@@ -4012,48 +3906,6 @@
     <t>{
   "selected_filter": {
     "Cancer type": "Melanoma",
-    "Clinical setting in relation to surgery": "Adjuvant",
-    "Class of ICI": "PD-1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Melanoma",
-    "Monotherapy/combination": "Combination",
-    "Type of combination": "ICI + ICI"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Clinical setting in relation to surgery",
-    "Column 6": "Study name",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Class of ICI",
-    "Column 9": "Name of ICI",
-    "Column 10": "Trial phase"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Gastric/GEJ",
     "Class of ICI": "CTLA-4"
   },
   "selected_column": {
@@ -4061,394 +3913,20 @@
     "Column 2": "PMID",
     "Column 3": "Authors",
     "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Total sample size",
-    "Column 7": "Class of ICI",
-    "Column 8": "Trial phase",
-    "Column 9": "Study name",
-    "Column 10": "Name of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Renal Cell Carcinoma (RCC)",
-    "Class of ICI": "PD-1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Study name",
-    "Column 9": "Trial phase",
-    "Column 10": "Control regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "CTLA-4",
-    "Monotherapy/combination": "Combination"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Study name",
-    "Column 8": "Class of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Type of combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Trial phase": "Phase 3",
-    "Monotherapy/combination": "Monotherapy",
-    "Clinical setting in relation to surgery": "Maintenance",
-    "Class of ICI": "PD-L1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Name of ICI",
-    "Column 8": "Trial phase",
-    "Column 9": "Treatment regimen",
-    "Column 10": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Trial phase": "Phase 3",
-    "Class of ICI": "PD-1",
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Monotherapy/combination": "Combination"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Total sample size",
-    "Column 7": "Name of ICI",
-    "Column 8": "Trial phase",
-    "Column 9": "Study name",
-    "Column 10": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of control": "Chemo / Anti-EGFR"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Study name",
-    "Column 9": "Trial phase",
-    "Column 10": "Control regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Clinical setting in relation to surgery": "Neoadjuvant"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Name of ICI",
-    "Column 8": "Trial phase",
-    "Column 9": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Original/Follow up",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Trial phase",
-    "Column 8": "Study name",
-    "Column 9": "Name of ICI",
-    "Column 10": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Melanoma",
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
-    "Column 8": "Trial phase",
-    "Column 9": "Original/Follow up",
-    "Column 10": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Head and Neck (HNSCC)",
-    "Year": "2023+"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Type of Study": "Follow-up"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Trial phase",
-    "Column 7": "Original/Follow up",
-    "Column 8": "Study name",
-    "Column 9": "Name of ICI",
-    "Column 10": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Esophageal/GEJ",
-    "Class of ICI": "PD-1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Small Cell Lung Cancer (SCLC)"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Head and Neck (HNSCC)",
-    "Primary endpoint": "OS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Study name",
-    "Column 7": "Trial phase",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Melanoma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Name of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Monotherapy/combination"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Year": "2010–2012"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Class of ICI",
-    "Column 8": "Study name",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "PD-L1"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Study name",
-    "Column 6": "Name of ICI",
-    "Column 7": "Trial phase",
-    "Column 8": "Primary endpoint",
-    "Column 9": "Class of ICI",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Primary endpoint": "OS"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
-    "Column 6": "Trial phase",
-    "Column 7": "Study name",
-    "Column 8": "Name of ICI",
-    "Column 9": "Class of ICI",
-    "Column 10": "Treatment regimen"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Class of ICI": "PD-L1",
-    "Monotherapy/combination": "Combination"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Name of ICI",
-    "Column 6": "Primary endpoint",
-    "Column 7": "Study name",
-    "Column 8": "Class of ICI",
-    "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Mesothelioma"
-  },
-  "selected_column": {
-    "Column 1": "NCT",
-    "Column 2": "PMID",
-    "Column 3": "Authors",
-    "Column 4": "Year",
-    "Column 5": "Primary endpoint",
+    "Column 5": "Cancer type",
     "Column 6": "Study name",
     "Column 7": "Name of ICI",
     "Column 8": "Class of ICI",
     "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "selected_filter": {
-    "Cancer type": "Breast"
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -4456,11 +3934,682 @@
     "Column 3": "Authors",
     "Column 4": "Year",
     "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Lines of treatment",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Cancer type",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Follow-up duration for primary endpoint(s) in months",
+    "Column 6": "Type of follow-up given",
+    "Column 7": "Primary endpoint",
+    "Column 8": "Study name",
+    "Column 9": "Cancer type",
+    "Column 10": "Name of ICI"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Pembrolizumab",
+    "Cancer type": "Melanoma",
+    "Clinical Setting": "Adjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Clinical setting in relation to surgery",
+    "Column 8": "Trial phase",
+    "Column 9": "Study name",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "CTLA-4",
+    "Cancer type": "Gastric/GEJ"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Renal Cell Carcinoma (RCC)",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Class of ICI",
+    "Column 7": "Name of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "PD-L1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "CTLA-4",
+    "Monotherapy/combination": "Combination Therapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Monotherapy/combination",
+    "Column 7": "Type of combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Cancer type",
+    "Column 10": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Head and Neck (HNSCC)",
+    "Class of ICI": "PD-1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Class of ICI",
+    "Column 7": "Name of ICI",
+    "Column 8": "Trial phase",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Pembrolizumab",
+    "Cancer type": "NSCLC",
+    "Trial phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Trial phase",
+    "Column 7": "Name of ICI",
+    "Column 8": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Avelumab",
+    "Cancer type": "Urothelial"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Clinical setting in relation to surgery",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Durvalumab",
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Maintenance",
+    "Trial phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Clinical setting in relation to surgery",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial phase": "Phase 3",
+    "Class of ICI": "PD-1",
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Monotherapy/combination": "Combination Therapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Total sample size",
     "Column 6": "Primary endpoint",
+    "Column 7": "Trial phase",
+    "Column 8": "Class of ICI",
+    "Column 9": "Cancer type",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of combination (Treatment Arm)": "ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + TKI",
+    "Cancer type": "Renal Cell Carcinoma (RCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Type of combination",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + RadiatICln"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Type of combination (Treatment Arm)": "ICI + Vaccine"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Cancer type",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Interferon"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Cancer type",
+    "Column 7": "Trial phase",
+    "Column 8": "Name of ICI",
+    "Column 9": "Class of ICI",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Best Supportive Care (BSC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Type of control",
+    "Column 7": "Cancer type",
+    "Column 8": "Clinical setting in relation to surgery",
+    "Column 9": "Trial phase",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Chemo / Anti-EGFR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Cancer type",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "mTOR inhibitor",
+    "Cancer type": "Renal Cell Carcinoma (RCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Type of control",
+    "Column 7": "Cancer type",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Name of ICI",
+    "Column 10": "Class of ICI"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Multikinase inhibitor"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Type of control",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
+    "Column 9": "Study name",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "Path CR",
+    "Clinical Setting": "Neoadjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Clinical setting in relation to surgery",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
+    "Column 9": "Study name",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "ORR"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "PFS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
+    "Column 9": "Name of ICI",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "Safety"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Secondary endpoint",
+    "Column 7": "Trial phase",
+    "Column 8": "Total sample size",
+    "Column 9": "Study name",
+    "Column 10": "Original/Follow Up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Is PD-L1 positivity inclusion criteria",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Trial phase",
+    "Column 10": "Lines of treatment"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Multiple Myeloma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Trial phase",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Mesothelioma",
+    "Monotherapy/combination": "Combination Therapy",
+    "Type of combination (Treatment Arm)": "ICI + ICI"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Control regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Original/Follow Up",
+    "Column 6": "Study name",
+    "Column 7": "Trial phase",
+    "Column 8": "Cancer type",
+    "Column 9": "Type of follow-up given",
+    "Column 10": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Trial phase",
+    "Column 7": "Cancer type",
+    "Column 8": "Total sample size",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Primary multiple, composite, or co-primary endpoints?"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Trial phase",
+    "Column 8": "Total sample size",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "PFS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Follow-up duration for primary endpoint(s) in months",
+    "Column 7": "Study name",
+    "Column 8": "Type of follow-up given"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Number of arms",
+    "Column 6": "Name of ICI",
     "Column 7": "Class of ICI",
     "Column 8": "Study name",
+    "Column 9": "Cancer type",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Head and Neck (HNSCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
     "Column 9": "Trial phase",
-    "Column 10": "Cancer type"
+    "Column 10": "Clinical setting in relation to surgery"
   }
 }</t>
   </si>
@@ -4468,8 +4617,7 @@
     <t>{
   "selected_filter": {
     "Cancer type": "Melanoma",
-    "Clinical setting in relation to surgery": "Adjuvant",
-    "Class of ICI": "PD-1"
+    "Type of combination (Treatment Arm)": "ICI + ICI"
   },
   "selected_column": {
     "Column 1": "NCT",
@@ -4478,9 +4626,943 @@
     "Column 4": "Year",
     "Column 5": "Study name",
     "Column 6": "Name of ICI",
-    "Column 7": "Primary endpoint",
+    "Column 7": "Cancer type",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Type of combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Secondary endpoint",
+    "Column 6": "Primary endpoint",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
+    "Column 9": "Study name",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Original/Follow Up",
+    "Column 6": "Primary endpoint",
+    "Column 7": "Secondary endpoint",
+    "Column 8": "Type of follow-up given",
+    "Column 9": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Included in MA": "No"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Trial phase",
+    "Column 7": "Cancer type",
+    "Column 8": "Total sample size",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Original publication or Follow-up"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Renal Cell Carcinoma (RCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Original/Follow Up",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
     "Column 8": "Class of ICI",
-    "Column 9": "Trial phase"
+    "Column 9": "Trial phase",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial phase": "Phase 3",
+    "Cancer type": "Gastric/GEJ",
+    "Class of ICI": "PD-L1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Trial phase",
+    "Column 6": "Cancer type",
+    "Column 7": "Class of ICI",
+    "Column 8": "Name of ICI",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Head and Neck (HNSCC)",
+    "ICI Name": "['Pembrolizumab', 'Nivolumab']"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Class of ICI",
+    "Column 8": "Trial phase",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Breast",
+    "ICI Name": "Atezolizumab, Pembrolizumab"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Trial phase",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Hepatocellular carcinoma (HCC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Lines of treatment",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Renal Cell Carcinoma (RCC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "NSCLC",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Control regimen",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Is PD-L1 positivity inclusion criteria",
+    "Column 6": "Cancer type",
+    "Column 7": "Study name",
+    "Column 8": "Name of ICI",
+    "Column 9": "Class of ICI",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Small Cell Lung Cancer (SCLC)",
+    "Type of combination (Treatment Arm)": "ICI + Chemo",
+    "Class of ICI": "PD-L1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Type of combination",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Type of combination (Treatment Arm)": "ICI + ICI + Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Name of ICI",
+    "Column 8": "Class of ICI",
+    "Column 9": "Type of combination",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "CTLA-4",
+    "ICI Name": "Ipilimumab",
+    "Cancer type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Trial phase",
+    "Column 9": "Study name",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Class of ICI",
+    "Column 7": "Lines of treatment",
+    "Column 8": "Cancer type",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Trial phase",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Type of follow-up given",
+    "Column 10": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Pembrolizumab",
+    "Cancer type": "Melanoma",
+    "Clinical Setting": "Adjuvant"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Clinical setting in relation to surgery",
+    "Column 9": "Trial phase",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Class of ICI": "PD-1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Treatment regimen",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Cancer type",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Melanoma",
+    "Monotherapy/combination": "Combination Therapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Monotherapy/combination",
+    "Column 7": "Type of combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Class": "PD-L1"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
+    "Column 9": "Primary endpoint",
+    "Column 10": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS (Overall Survival)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Control regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "PD-1",
+    "Monotherapy/combination": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Primary endpoint",
+    "Column 9": "Secondary endpoint",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "CTLA-4",
+    "Monotherapy/combination": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Cancer type",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Nivolumab",
+    "Cancer type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Avelumab",
+    "Cancer type": "Urothelial"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Name of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Clinical setting in relation to surgery",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Trial phase",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Tremelimumab",
+    "Cancer type": "Hepatocellular carcinoma (HCC)",
+    "Type of combination (Treatment Arm)": "ICI + ICI",
+    "Class of ICI": "CTLA-4"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Monotherapy/combination",
+    "Column 9": "Type of combination",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Durvalumab",
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Maintenance",
+    "Control Arm": "Placebo",
+    "Trial phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Clinical setting in relation to surgery",
+    "Column 9": "Control regimen",
+    "Column 10": "Primary endpoint"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "PD-L1",
+    "Monotherapy/combination": "Monotherapy"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Monotherapy/combination",
+    "Column 7": "Cancer type"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Melanoma",
+    "Type of combination (Treatment Arm)": "ICI + BRAFi + MEKi"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Cancer type",
+    "Column 7": "Treatment regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Class of ICI",
+    "Column 10": "Type of combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Trial phase": "Phase 3",
+    "Control Arm": "Placebo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Trial phase",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Control regimen",
+    "Column 9": "Type of control",
+    "Column 10": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Control Arm": "Chemo"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Control regimen",
+    "Column 7": "Type of control",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Trial phase",
+    "Column 10": "Study name"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Control Arm": "Vaccine"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Control regimen",
+    "Column 6": "Type of control",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
+    "Column 9": "Study name",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Total sample size"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "EFS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Primary endpoint",
+    "Column 6": "Primary multiple, composite, or co-primary endpoints?",
+    "Column 7": "Cancer type",
+    "Column 8": "Trial phase",
+    "Column 9": "Total sample size",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Prostate",
+    "Is any other biomarker used for inclusion": "Yes"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Is PD-L1 positivity inclusion criteria",
+    "Column 9": "Is any other biomarker used for inclusion",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Mesothelioma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Treatment regimen",
+    "Column 7": "Control regimen",
+    "Column 8": "Name of ICI",
+    "Column 9": "Class of ICI",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Melanoma"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Original publication or Follow-up",
+    "Column 6": "Study name",
+    "Column 7": "Cancer type",
+    "Column 8": "Name of ICI",
+    "Column 9": "Class of ICI",
+    "Column 10": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Clinical Setting": "Metastatic / Recurrent (Unresectable)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Lines of treatment",
+    "Column 9": "Clinical setting in relation to surgery",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "ICI Name": "Pembrolizumab",
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)",
+    "Control Arm": "Chemo",
+    "Trial phase": "Phase 3"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Study name",
+    "Column 6": "Name of ICI",
+    "Column 7": "Cancer type",
+    "Column 8": "Control regimen",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Primary Endpoint": "OS"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Original/Follow Up",
+    "Column 6": "Primary endpoint",
+    "Column 7": "Secondary endpoint",
+    "Column 8": "Type of follow-up given",
+    "Column 9": "Follow-up duration for primary endpoint(s) in months"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Class of ICI": "PD-1",
+    "Cancer type": "Esophageal/GEJ"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Cancer type",
+    "Column 7": "Name of ICI",
+    "Column 8": "Trial phase",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Clinical setting in relation to surgery"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Breast"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Trial phase",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Treatment regimen"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Hepatocellular carcinoma (HCC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Lines of treatment",
+    "Column 7": "Name of ICI",
+    "Column 8": "Treatment regimen",
+    "Column 9": "Control regimen",
+    "Column 10": "Monotherapy/combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Clinical Setting": "Perioperative"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Clinical setting in relation to surgery",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Cancer type",
+    "Column 9": "Monotherapy/combination",
+    "Column 10": "Type of combination"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Non-Small Cell Lung Cancer (NSCLC)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Class of ICI",
+    "Column 6": "Name of ICI",
+    "Column 7": "Monotherapy/combination",
+    "Column 8": "Type of combination",
+    "Column 9": "Control regimen",
+    "Column 10": "Is PD-L1 positivity inclusion criteria"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {
+    "Cancer type": "Renal Cell Carcinoma (RCC)",
+    "Type of combination (Treatment Arm)": "ICI + TKI (Tyrosine Kinase Inhibitor)"
+  },
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Type of combination",
+    "Column 9": "Treatment regimen",
+    "Column 10": "Trial phase"
+  }
+}</t>
+  </si>
+  <si>
+    <t>{
+  "selected_filter": {},
+  "selected_column": {
+    "Column 1": "NCT",
+    "Column 2": "PMID",
+    "Column 3": "Authors",
+    "Column 4": "Year",
+    "Column 5": "Cancer type",
+    "Column 6": "Name of ICI",
+    "Column 7": "Class of ICI",
+    "Column 8": "Trial phase",
+    "Column 9": "Study name",
+    "Column 10": "Primary endpoint"
   }
 }</t>
   </si>
@@ -4874,7 +5956,7 @@
         <v>205</v>
       </c>
       <c r="E2" t="s">
-        <v>205</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4888,10 +5970,10 @@
         <v>206</v>
       </c>
       <c r="D3" t="s">
-        <v>305</v>
+        <v>206</v>
       </c>
       <c r="E3" t="s">
-        <v>305</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4905,10 +5987,10 @@
         <v>207</v>
       </c>
       <c r="D4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E4" t="s">
-        <v>306</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4956,7 +6038,7 @@
         <v>210</v>
       </c>
       <c r="D7" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E7" t="s">
         <v>210</v>
@@ -4973,10 +6055,10 @@
         <v>211</v>
       </c>
       <c r="D8" t="s">
-        <v>211</v>
+        <v>307</v>
       </c>
       <c r="E8" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -5007,10 +6089,10 @@
         <v>213</v>
       </c>
       <c r="D10" t="s">
-        <v>213</v>
+        <v>308</v>
       </c>
       <c r="E10" t="s">
-        <v>323</v>
+        <v>359</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -5044,7 +6126,7 @@
         <v>215</v>
       </c>
       <c r="E12" t="s">
-        <v>215</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -5061,7 +6143,7 @@
         <v>216</v>
       </c>
       <c r="E13" t="s">
-        <v>324</v>
+        <v>216</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -5078,7 +6160,7 @@
         <v>217</v>
       </c>
       <c r="E14" t="s">
-        <v>217</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -5092,10 +6174,10 @@
         <v>218</v>
       </c>
       <c r="D15" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E15" t="s">
-        <v>218</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -5109,7 +6191,7 @@
         <v>219</v>
       </c>
       <c r="D16" t="s">
-        <v>219</v>
+        <v>310</v>
       </c>
       <c r="E16" t="s">
         <v>219</v>
@@ -5126,10 +6208,10 @@
         <v>220</v>
       </c>
       <c r="D17" t="s">
-        <v>220</v>
+        <v>311</v>
       </c>
       <c r="E17" t="s">
-        <v>220</v>
+        <v>311</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -5146,7 +6228,7 @@
         <v>221</v>
       </c>
       <c r="E18" t="s">
-        <v>221</v>
+        <v>362</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -5177,10 +6259,10 @@
         <v>223</v>
       </c>
       <c r="D20" t="s">
-        <v>223</v>
+        <v>312</v>
       </c>
       <c r="E20" t="s">
-        <v>223</v>
+        <v>363</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -5197,7 +6279,7 @@
         <v>224</v>
       </c>
       <c r="E21" t="s">
-        <v>224</v>
+        <v>364</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -5211,10 +6293,10 @@
         <v>225</v>
       </c>
       <c r="D22" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E22" t="s">
-        <v>309</v>
+        <v>365</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -5228,10 +6310,10 @@
         <v>226</v>
       </c>
       <c r="D23" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E23" t="s">
-        <v>226</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -5248,7 +6330,7 @@
         <v>227</v>
       </c>
       <c r="E24" t="s">
-        <v>227</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -5279,10 +6361,10 @@
         <v>229</v>
       </c>
       <c r="D26" t="s">
-        <v>229</v>
+        <v>315</v>
       </c>
       <c r="E26" t="s">
-        <v>229</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -5296,7 +6378,7 @@
         <v>230</v>
       </c>
       <c r="D27" t="s">
-        <v>230</v>
+        <v>316</v>
       </c>
       <c r="E27" t="s">
         <v>230</v>
@@ -5313,10 +6395,10 @@
         <v>231</v>
       </c>
       <c r="D28" t="s">
-        <v>231</v>
+        <v>317</v>
       </c>
       <c r="E28" t="s">
-        <v>231</v>
+        <v>317</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -5330,10 +6412,10 @@
         <v>232</v>
       </c>
       <c r="D29" t="s">
-        <v>232</v>
+        <v>318</v>
       </c>
       <c r="E29" t="s">
-        <v>232</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -5350,7 +6432,7 @@
         <v>233</v>
       </c>
       <c r="E30" t="s">
-        <v>233</v>
+        <v>367</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -5418,7 +6500,7 @@
         <v>237</v>
       </c>
       <c r="E34" t="s">
-        <v>237</v>
+        <v>368</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -5435,7 +6517,7 @@
         <v>238</v>
       </c>
       <c r="E35" t="s">
-        <v>238</v>
+        <v>369</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -5466,7 +6548,7 @@
         <v>240</v>
       </c>
       <c r="D37" t="s">
-        <v>240</v>
+        <v>319</v>
       </c>
       <c r="E37" t="s">
         <v>240</v>
@@ -5483,10 +6565,10 @@
         <v>241</v>
       </c>
       <c r="D38" t="s">
-        <v>241</v>
+        <v>320</v>
       </c>
       <c r="E38" t="s">
-        <v>241</v>
+        <v>320</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -5500,7 +6582,7 @@
         <v>242</v>
       </c>
       <c r="D39" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="E39" t="s">
         <v>242</v>
@@ -5534,10 +6616,10 @@
         <v>244</v>
       </c>
       <c r="D41" t="s">
-        <v>244</v>
+        <v>322</v>
       </c>
       <c r="E41" t="s">
-        <v>244</v>
+        <v>322</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -5551,7 +6633,7 @@
         <v>245</v>
       </c>
       <c r="D42" t="s">
-        <v>245</v>
+        <v>323</v>
       </c>
       <c r="E42" t="s">
         <v>245</v>
@@ -5571,7 +6653,7 @@
         <v>246</v>
       </c>
       <c r="E43" t="s">
-        <v>246</v>
+        <v>370</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -5619,7 +6701,7 @@
         <v>249</v>
       </c>
       <c r="D46" t="s">
-        <v>312</v>
+        <v>249</v>
       </c>
       <c r="E46" t="s">
         <v>249</v>
@@ -5636,10 +6718,10 @@
         <v>250</v>
       </c>
       <c r="D47" t="s">
-        <v>250</v>
+        <v>324</v>
       </c>
       <c r="E47" t="s">
-        <v>250</v>
+        <v>324</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -5653,10 +6735,10 @@
         <v>251</v>
       </c>
       <c r="D48" t="s">
-        <v>251</v>
+        <v>325</v>
       </c>
       <c r="E48" t="s">
-        <v>251</v>
+        <v>325</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -5673,7 +6755,7 @@
         <v>252</v>
       </c>
       <c r="E49" t="s">
-        <v>252</v>
+        <v>371</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -5687,7 +6769,7 @@
         <v>253</v>
       </c>
       <c r="D50" t="s">
-        <v>253</v>
+        <v>326</v>
       </c>
       <c r="E50" t="s">
         <v>253</v>
@@ -5724,7 +6806,7 @@
         <v>255</v>
       </c>
       <c r="E52" t="s">
-        <v>255</v>
+        <v>372</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -5738,7 +6820,7 @@
         <v>256</v>
       </c>
       <c r="D53" t="s">
-        <v>256</v>
+        <v>327</v>
       </c>
       <c r="E53" t="s">
         <v>256</v>
@@ -5755,7 +6837,7 @@
         <v>257</v>
       </c>
       <c r="D54" t="s">
-        <v>257</v>
+        <v>328</v>
       </c>
       <c r="E54" t="s">
         <v>257</v>
@@ -5809,7 +6891,7 @@
         <v>260</v>
       </c>
       <c r="E57" t="s">
-        <v>260</v>
+        <v>373</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -5823,7 +6905,7 @@
         <v>261</v>
       </c>
       <c r="D58" t="s">
-        <v>261</v>
+        <v>329</v>
       </c>
       <c r="E58" t="s">
         <v>261</v>
@@ -5840,10 +6922,10 @@
         <v>262</v>
       </c>
       <c r="D59" t="s">
-        <v>262</v>
+        <v>330</v>
       </c>
       <c r="E59" t="s">
-        <v>325</v>
+        <v>374</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -5857,10 +6939,10 @@
         <v>263</v>
       </c>
       <c r="D60" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E60" t="s">
-        <v>313</v>
+        <v>263</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -5874,10 +6956,10 @@
         <v>264</v>
       </c>
       <c r="D61" t="s">
-        <v>314</v>
+        <v>264</v>
       </c>
       <c r="E61" t="s">
-        <v>314</v>
+        <v>375</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -5891,10 +6973,10 @@
         <v>265</v>
       </c>
       <c r="D62" t="s">
-        <v>265</v>
+        <v>332</v>
       </c>
       <c r="E62" t="s">
-        <v>265</v>
+        <v>332</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -5908,10 +6990,10 @@
         <v>266</v>
       </c>
       <c r="D63" t="s">
-        <v>266</v>
+        <v>333</v>
       </c>
       <c r="E63" t="s">
-        <v>266</v>
+        <v>333</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -5925,7 +7007,7 @@
         <v>267</v>
       </c>
       <c r="D64" t="s">
-        <v>267</v>
+        <v>334</v>
       </c>
       <c r="E64" t="s">
         <v>267</v>
@@ -5942,7 +7024,7 @@
         <v>268</v>
       </c>
       <c r="D65" t="s">
-        <v>268</v>
+        <v>335</v>
       </c>
       <c r="E65" t="s">
         <v>268</v>
@@ -5962,7 +7044,7 @@
         <v>269</v>
       </c>
       <c r="E66" t="s">
-        <v>269</v>
+        <v>376</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -5993,10 +7075,10 @@
         <v>271</v>
       </c>
       <c r="D68" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
       <c r="E68" t="s">
-        <v>315</v>
+        <v>336</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -6013,7 +7095,7 @@
         <v>272</v>
       </c>
       <c r="E69" t="s">
-        <v>272</v>
+        <v>377</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -6027,7 +7109,7 @@
         <v>273</v>
       </c>
       <c r="D70" t="s">
-        <v>273</v>
+        <v>337</v>
       </c>
       <c r="E70" t="s">
         <v>273</v>
@@ -6044,7 +7126,7 @@
         <v>274</v>
       </c>
       <c r="D71" t="s">
-        <v>274</v>
+        <v>338</v>
       </c>
       <c r="E71" t="s">
         <v>274</v>
@@ -6061,10 +7143,10 @@
         <v>275</v>
       </c>
       <c r="D72" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="E72" t="s">
-        <v>275</v>
+        <v>378</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -6095,7 +7177,7 @@
         <v>277</v>
       </c>
       <c r="D74" t="s">
-        <v>277</v>
+        <v>340</v>
       </c>
       <c r="E74" t="s">
         <v>277</v>
@@ -6112,7 +7194,7 @@
         <v>278</v>
       </c>
       <c r="D75" t="s">
-        <v>278</v>
+        <v>341</v>
       </c>
       <c r="E75" t="s">
         <v>278</v>
@@ -6129,7 +7211,7 @@
         <v>279</v>
       </c>
       <c r="D76" t="s">
-        <v>279</v>
+        <v>342</v>
       </c>
       <c r="E76" t="s">
         <v>279</v>
@@ -6146,10 +7228,10 @@
         <v>280</v>
       </c>
       <c r="D77" t="s">
-        <v>317</v>
+        <v>280</v>
       </c>
       <c r="E77" t="s">
-        <v>280</v>
+        <v>379</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -6163,10 +7245,10 @@
         <v>281</v>
       </c>
       <c r="D78" t="s">
-        <v>318</v>
+        <v>281</v>
       </c>
       <c r="E78" t="s">
-        <v>318</v>
+        <v>281</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -6180,7 +7262,7 @@
         <v>282</v>
       </c>
       <c r="D79" t="s">
-        <v>319</v>
+        <v>282</v>
       </c>
       <c r="E79" t="s">
         <v>282</v>
@@ -6197,7 +7279,7 @@
         <v>283</v>
       </c>
       <c r="D80" t="s">
-        <v>283</v>
+        <v>343</v>
       </c>
       <c r="E80" t="s">
         <v>283</v>
@@ -6214,10 +7296,10 @@
         <v>284</v>
       </c>
       <c r="D81" t="s">
-        <v>284</v>
+        <v>344</v>
       </c>
       <c r="E81" t="s">
-        <v>326</v>
+        <v>380</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -6248,10 +7330,10 @@
         <v>286</v>
       </c>
       <c r="D83" t="s">
-        <v>286</v>
+        <v>345</v>
       </c>
       <c r="E83" t="s">
-        <v>286</v>
+        <v>381</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -6265,7 +7347,7 @@
         <v>287</v>
       </c>
       <c r="D84" t="s">
-        <v>287</v>
+        <v>346</v>
       </c>
       <c r="E84" t="s">
         <v>287</v>
@@ -6285,7 +7367,7 @@
         <v>288</v>
       </c>
       <c r="E85" t="s">
-        <v>288</v>
+        <v>382</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -6299,7 +7381,7 @@
         <v>289</v>
       </c>
       <c r="D86" t="s">
-        <v>289</v>
+        <v>347</v>
       </c>
       <c r="E86" t="s">
         <v>289</v>
@@ -6350,10 +7432,10 @@
         <v>292</v>
       </c>
       <c r="D89" t="s">
-        <v>292</v>
+        <v>348</v>
       </c>
       <c r="E89" t="s">
-        <v>292</v>
+        <v>383</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -6367,7 +7449,7 @@
         <v>293</v>
       </c>
       <c r="D90" t="s">
-        <v>320</v>
+        <v>293</v>
       </c>
       <c r="E90" t="s">
         <v>293</v>
@@ -6401,7 +7483,7 @@
         <v>295</v>
       </c>
       <c r="D92" t="s">
-        <v>295</v>
+        <v>349</v>
       </c>
       <c r="E92" t="s">
         <v>295</v>
@@ -6438,7 +7520,7 @@
         <v>297</v>
       </c>
       <c r="E94" t="s">
-        <v>297</v>
+        <v>384</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -6452,7 +7534,7 @@
         <v>298</v>
       </c>
       <c r="D95" t="s">
-        <v>298</v>
+        <v>350</v>
       </c>
       <c r="E95" t="s">
         <v>298</v>
@@ -6469,10 +7551,10 @@
         <v>299</v>
       </c>
       <c r="D96" t="s">
-        <v>299</v>
+        <v>351</v>
       </c>
       <c r="E96" t="s">
-        <v>299</v>
+        <v>351</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -6486,10 +7568,10 @@
         <v>300</v>
       </c>
       <c r="D97" t="s">
-        <v>321</v>
+        <v>352</v>
       </c>
       <c r="E97" t="s">
-        <v>300</v>
+        <v>385</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -6520,10 +7602,10 @@
         <v>302</v>
       </c>
       <c r="D99" t="s">
-        <v>302</v>
+        <v>353</v>
       </c>
       <c r="E99" t="s">
-        <v>302</v>
+        <v>353</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -6537,7 +7619,7 @@
         <v>303</v>
       </c>
       <c r="D100" t="s">
-        <v>303</v>
+        <v>354</v>
       </c>
       <c r="E100" t="s">
         <v>303</v>
@@ -6554,10 +7636,10 @@
         <v>304</v>
       </c>
       <c r="D101" t="s">
-        <v>304</v>
+        <v>355</v>
       </c>
       <c r="E101" t="s">
-        <v>327</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
